--- a/uploads/2025/May/1/expt_data/HYP_collated_May25.xlsx
+++ b/uploads/2025/May/1/expt_data/HYP_collated_May25.xlsx
@@ -1,23 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28830"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://luky-my.sharepoint.com/personal/ugu222_uky_edu/Documents/Temp/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_514DF0170F1E475E2F67D3E5F4012D16118A1C69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F8A6CC-8D67-436B-BEFA-839A1CE730B2}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28908"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A645CF2F6CE5E19485E0EE65C0E1D549FB5B3C3A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9100BDC-9840-40BC-B05D-B80C234CC422}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$78</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="95">
   <si>
     <t>Hashcode</t>
   </si>
@@ -48,6 +40,9 @@
   </si>
   <si>
     <t>Specimen_No</t>
+  </si>
+  <si>
+    <t>Experiment_Date</t>
   </si>
   <si>
     <t>lab_archives_link</t>
@@ -341,7 +336,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -353,8 +355,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,39 +386,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -467,7 +470,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -578,6 +581,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -586,13 +596,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -657,31 +660,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -689,20 +672,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="126" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="133.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,1793 +707,2024 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>50242.1</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
+      <c r="D2" s="1">
+        <v>45377</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
         <v>3.7914532630000002</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>28.084838990000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>50251.1</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
+      <c r="D3" s="1">
+        <v>45315</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
         <v>13.392399879999999</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>99.202962040000003</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>50278.1</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
+      <c r="D4" s="1">
+        <v>45314</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
         <v>21.382646279999999</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>158.3899725</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>54227.1</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
+      <c r="D5" s="1">
+        <v>45315</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>3.683573473</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>27.28572943</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>50313.1</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
+      <c r="D6" s="1">
+        <v>45378</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>9.3027133249999991</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>68.908987589999995</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>50391.199999999997</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
+      <c r="D7" s="1">
+        <v>45447</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7">
         <v>4.5169718210000003</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>33.459050529999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>50538.2</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
+      <c r="D8" s="1">
+        <v>45378</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>4.3113857739999997</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>31.936190920000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>50823.199999999997</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
+      <c r="D9" s="1">
+        <v>45315</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
         <v>5.1533776360000001</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>38.173167669999998</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10">
         <v>54230.1</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
+      <c r="D10" s="1">
+        <v>45315</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
         <v>5.5602340589999999</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>41.186918949999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
       <c r="C11">
         <v>50792.1</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
+      <c r="D11" s="1">
+        <v>45314</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
         <v>7.7129404350000002</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>57.13289211</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>50544.1</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
+      <c r="D12" s="1">
+        <v>45315</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
         <v>6.6382986280000003</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>49.172582429999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>50850.1</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
+      <c r="D13" s="1">
+        <v>45378</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
         <v>15.12863486</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>112.0639619</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>50987.1</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
+      <c r="D14" s="1">
+        <v>45378</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
         <v>5.6236037449999996</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>41.656324040000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>51003.1</v>
       </c>
-      <c r="D15" t="s">
-        <v>9</v>
+      <c r="D15" s="1">
+        <v>45378</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
         <v>1.1046023199999999</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>8.1822394109999994</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16">
         <v>51223.1</v>
       </c>
-      <c r="D16" t="s">
-        <v>9</v>
+      <c r="D16" s="1">
+        <v>45314</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
         <v>5.48818451</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>40.653218590000002</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>51230.400000000001</v>
       </c>
-      <c r="D17" t="s">
-        <v>9</v>
+      <c r="D17" s="1">
+        <v>45377</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
         <v>5.0518447069999999</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>37.421071900000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>51236.7</v>
       </c>
-      <c r="D18" t="s">
-        <v>9</v>
+      <c r="D18" s="1">
+        <v>45377</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
         <v>13.580804690000001</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>100.59855330000001</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>51317.2</v>
       </c>
-      <c r="D19" t="s">
-        <v>9</v>
+      <c r="D19" s="1">
+        <v>45378</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
         <v>6.9483409680000001</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>51.46919235</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>51736.1</v>
       </c>
-      <c r="D20" t="s">
-        <v>9</v>
+      <c r="D20" s="1">
+        <v>45315</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
         <v>7.3620668849999999</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>54.53382878</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>51435.199999999997</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
+      <c r="D21" s="1">
+        <v>45377</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
         <v>24.25509044</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>179.6673366</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>51454.400000000001</v>
       </c>
-      <c r="D22" t="s">
-        <v>9</v>
+      <c r="D22" s="1">
+        <v>45377</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
         <v>5.7040545659999999</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>42.25225605</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>51474.1</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
+      <c r="D23" s="1">
+        <v>45377</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
         <v>4.6193196719999996</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>34.21718276</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>51490.6</v>
       </c>
-      <c r="D24" t="s">
-        <v>9</v>
+      <c r="D24" s="1">
+        <v>45314</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
         <v>5.2873619300000003</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>39.165643930000002</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25">
         <v>51501.5</v>
       </c>
-      <c r="D25" t="s">
-        <v>9</v>
+      <c r="D25" s="1">
+        <v>45314</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
         <v>8.3398783739999995</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>61.776876850000001</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>51734.1</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
+      <c r="D26" s="1">
+        <v>45315</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
         <v>2.4430607219999998</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>18.09674609</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>51705.1</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
+      <c r="D27" s="1">
+        <v>45378</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
         <v>50.993194000000003</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>377.7273629</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>51707.1</v>
       </c>
-      <c r="D28" t="s">
-        <v>9</v>
+      <c r="D28" s="1">
+        <v>45377</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
         <v>22.757766759999999</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>168.5760501</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29">
         <v>51515.3</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
+      <c r="D29" s="1">
+        <v>45315</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
         <v>3.6188354820000002</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>26.806188760000001</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>51333.3</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
+      <c r="D30" s="1">
+        <v>45315</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
         <v>13.37956299</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>99.107873999999995</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31">
         <v>51737.1</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
+      <c r="D31" s="1">
+        <v>45314</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
         <v>8.8402380669999996</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>65.483244940000006</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32">
         <v>51738.1</v>
       </c>
-      <c r="D32" t="s">
-        <v>9</v>
+      <c r="D32" s="1">
+        <v>45314</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
         <v>5.6408808180000003</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>41.784302349999997</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33">
         <v>51751.1</v>
       </c>
-      <c r="D33" t="s">
-        <v>9</v>
+      <c r="D33" s="1">
+        <v>45314</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
         <v>4.3331524750000003</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>32.097425739999998</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34">
         <v>51768.1</v>
       </c>
-      <c r="D34" t="s">
-        <v>9</v>
+      <c r="D34" s="1">
+        <v>45314</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
         <v>6.8883098900000004</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>51.024517699999997</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35">
         <v>51781.2</v>
       </c>
-      <c r="D35" t="s">
-        <v>9</v>
+      <c r="D35" s="1">
+        <v>45377</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
         <v>10.743443750000001</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>79.581064799999993</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36">
         <v>51791.3</v>
       </c>
-      <c r="D36" t="s">
-        <v>9</v>
+      <c r="D36" s="1">
+        <v>45314</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
         <v>4.6854596639999997</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>34.70710862</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C37">
         <v>51891.1</v>
       </c>
-      <c r="D37" t="s">
-        <v>9</v>
+      <c r="D37" s="1">
+        <v>45314</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
         <v>7.1607050650000001</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>53.042259739999999</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38">
         <v>51898.1</v>
       </c>
-      <c r="D38" t="s">
-        <v>9</v>
+      <c r="D38" s="1">
+        <v>45378</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
         <v>0.70241427199999995</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>5.2030686819999996</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>51923.3</v>
       </c>
-      <c r="D39" t="s">
-        <v>9</v>
+      <c r="D39" s="1">
+        <v>45378</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39">
         <v>10.981881339999999</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>81.347269209999993</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>51941.3</v>
       </c>
-      <c r="D40" t="s">
-        <v>9</v>
+      <c r="D40" s="1">
+        <v>45314</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
         <v>4.5166616250000002</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>33.456752780000002</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41">
         <v>51971.1</v>
       </c>
-      <c r="D41" t="s">
-        <v>9</v>
+      <c r="D41" s="1">
+        <v>45378</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41">
         <v>10.62250661</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>78.685234179999995</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>51982.2</v>
       </c>
-      <c r="D42" t="s">
-        <v>9</v>
+      <c r="D42" s="1">
+        <v>45314</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42">
         <v>5.4872534530000001</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>40.646321870000001</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43">
         <v>52080.3</v>
       </c>
-      <c r="D43" t="s">
-        <v>9</v>
+      <c r="D43" s="1">
+        <v>45378</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43">
         <v>10.97273624</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>81.279527700000003</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44">
         <v>54228.2</v>
       </c>
-      <c r="D44" t="s">
-        <v>9</v>
+      <c r="D44" s="1">
+        <v>45315</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44">
         <v>3.7396240559999998</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>27.70091893</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45">
         <v>52090.1</v>
       </c>
-      <c r="D45" t="s">
-        <v>9</v>
+      <c r="D45" s="1">
+        <v>45377</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45">
         <v>18.37364285</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>136.10105809999999</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46">
         <v>52240.4</v>
       </c>
-      <c r="D46" t="s">
-        <v>9</v>
+      <c r="D46" s="1">
+        <v>45447</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46">
         <v>3.6660237609999999</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>27.15573156</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47">
         <v>52252.1</v>
       </c>
-      <c r="D47" t="s">
-        <v>9</v>
+      <c r="D47" s="1">
+        <v>45377</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
         <v>18.38353218</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>136.17431239999999</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48">
         <v>52259.6</v>
       </c>
-      <c r="D48" t="s">
-        <v>9</v>
+      <c r="D48" s="1">
+        <v>45447</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48">
         <v>4.7441379000000001</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>35.141762219999997</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C49">
         <v>52621.3</v>
       </c>
-      <c r="D49" t="s">
-        <v>9</v>
+      <c r="D49" s="1">
+        <v>45447</v>
       </c>
       <c r="E49" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49">
         <v>5.8581364669999996</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>43.393603460000001</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50">
         <v>52703.199999999997</v>
       </c>
-      <c r="D50" t="s">
-        <v>9</v>
+      <c r="D50" s="1">
+        <v>45447</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50">
         <v>8.9698934920000006</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>66.443655489999998</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C51">
         <v>52745.2</v>
       </c>
-      <c r="D51" t="s">
-        <v>9</v>
+      <c r="D51" s="1">
+        <v>45314</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
         <v>9.1225181299999996</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>67.574208369999994</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C52">
         <v>52754.2</v>
       </c>
-      <c r="D52" t="s">
-        <v>9</v>
+      <c r="D52" s="1">
+        <v>45377</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
         <v>32.62933821</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>241.6988015</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C53">
         <v>53026.6</v>
       </c>
-      <c r="D53" t="s">
-        <v>9</v>
+      <c r="D53" s="1">
+        <v>45447</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>63</v>
+      </c>
+      <c r="G53">
         <v>4.8618549690000004</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>36.013740509999998</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C54">
         <v>53074.5</v>
       </c>
-      <c r="D54" t="s">
-        <v>9</v>
+      <c r="D54" s="1">
+        <v>45447</v>
       </c>
       <c r="E54" t="s">
-        <v>65</v>
-      </c>
-      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G54">
         <v>2.3343706919999998</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>17.291634760000001</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C55">
         <v>53131.4</v>
       </c>
-      <c r="D55" t="s">
-        <v>9</v>
+      <c r="D55" s="1">
+        <v>45447</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>63</v>
+      </c>
+      <c r="G55">
         <v>2.78830986</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>20.65414711</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C56">
         <v>53229.5</v>
       </c>
-      <c r="D56" t="s">
-        <v>9</v>
+      <c r="D56" s="1">
+        <v>45447</v>
       </c>
       <c r="E56" t="s">
-        <v>65</v>
-      </c>
-      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56">
         <v>5.0853311229999996</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>37.669119430000002</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57">
         <v>53237.5</v>
       </c>
-      <c r="D57" t="s">
-        <v>9</v>
+      <c r="D57" s="1">
+        <v>45447</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57">
         <v>6.2646543430000001</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>46.404846980000002</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C58">
         <v>53657.1</v>
       </c>
-      <c r="D58" t="s">
-        <v>9</v>
+      <c r="D58" s="1">
+        <v>45377</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
         <v>11.95343765</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>88.543982569999997</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C59">
         <v>53659.1</v>
       </c>
-      <c r="D59" t="s">
-        <v>9</v>
+      <c r="D59" s="1">
+        <v>45378</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
         <v>18.6150126</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>137.88898219999999</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60">
         <v>54226.1</v>
       </c>
-      <c r="D60" t="s">
-        <v>9</v>
+      <c r="D60" s="1">
+        <v>45377</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60">
         <v>4.431476569</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>32.825752369999996</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C61">
         <v>50308.2</v>
       </c>
-      <c r="D61" t="s">
-        <v>9</v>
+      <c r="D61" s="1">
+        <v>45315</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61">
         <v>4.3028680369999996</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>31.873096570000001</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C62">
         <v>52082.2</v>
       </c>
-      <c r="D62" t="s">
-        <v>9</v>
+      <c r="D62" s="1">
+        <v>45315</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62">
         <v>9.4502806649999993</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>70.002078999999995</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>50572.1</v>
       </c>
-      <c r="D63" t="s">
-        <v>9</v>
+      <c r="D63" s="1">
+        <v>45315</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63">
         <v>4.3366239320000002</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>32.123140239999998</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C64">
         <v>54250.1</v>
       </c>
-      <c r="D64" t="s">
-        <v>9</v>
+      <c r="D64" s="1">
+        <v>45377</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64">
         <v>3.3308360499999998</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>24.672859630000001</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C65">
         <v>54264.2</v>
       </c>
-      <c r="D65" t="s">
-        <v>9</v>
+      <c r="D65" s="1">
+        <v>45314</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65">
         <v>6.756280437</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>50.046521759999997</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66">
         <v>54273.1</v>
       </c>
-      <c r="D66" t="s">
-        <v>9</v>
+      <c r="D66" s="1">
+        <v>45447</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
-      </c>
-      <c r="F66">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66">
         <v>4.690858746</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>34.747101819999997</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67">
         <v>58557.1</v>
       </c>
-      <c r="D67" t="s">
-        <v>9</v>
+      <c r="D67" s="1">
+        <v>45314</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67">
         <v>7.9023300279999997</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>58.53577799</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68">
         <v>73574.2</v>
       </c>
-      <c r="D68" t="s">
-        <v>9</v>
+      <c r="D68" s="1">
+        <v>45447</v>
       </c>
       <c r="E68" t="s">
-        <v>62</v>
-      </c>
-      <c r="F68">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>63</v>
+      </c>
+      <c r="G68">
         <v>4.9657624880000002</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>36.78342584</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69">
         <v>73654.100000000006</v>
       </c>
-      <c r="D69" t="s">
-        <v>9</v>
+      <c r="D69" s="1">
+        <v>45378</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69">
         <v>7.3011034669999999</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>54.082247899999999</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70">
         <v>83289.2</v>
       </c>
-      <c r="D70" t="s">
-        <v>9</v>
+      <c r="D70" s="1">
+        <v>45378</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70">
         <v>8.9794191029999997</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>66.514215579999998</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71">
         <v>83679.7</v>
       </c>
-      <c r="D71" t="s">
-        <v>9</v>
+      <c r="D71" s="1">
+        <v>45315</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71">
         <v>11.53076733</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>85.413091320000007</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72">
         <v>84322.6</v>
       </c>
-      <c r="D72" t="s">
-        <v>9</v>
+      <c r="D72" s="1">
+        <v>45315</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72">
         <v>16.87912987</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>125.03059159999999</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73">
         <v>84171.1</v>
       </c>
-      <c r="D73" t="s">
-        <v>9</v>
+      <c r="D73" s="1">
+        <v>45378</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73">
         <v>17.021471439999999</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>126.0849736</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C74">
         <v>84268.1</v>
       </c>
-      <c r="D74" t="s">
-        <v>9</v>
+      <c r="D74" s="1">
+        <v>45447</v>
       </c>
       <c r="E74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F74">
+        <v>10</v>
+      </c>
+      <c r="F74" t="s">
+        <v>66</v>
+      </c>
+      <c r="G74">
         <v>6.1227803810000001</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>45.353928750000001</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75">
         <v>83996.1</v>
       </c>
-      <c r="D75" t="s">
-        <v>9</v>
+      <c r="D75" s="1">
+        <v>45315</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75">
         <v>19.23053913</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>142.44843800000001</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C76">
         <v>84356.1</v>
       </c>
-      <c r="D76" t="s">
-        <v>9</v>
+      <c r="D76" s="1">
+        <v>45447</v>
       </c>
       <c r="E76" t="s">
-        <v>18</v>
-      </c>
-      <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="F76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76">
         <v>5.5416039359999996</v>
       </c>
-      <c r="G76">
+      <c r="H76">
         <v>41.048918039999997</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B77" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C77">
         <v>86789.3</v>
       </c>
-      <c r="D77" t="s">
-        <v>9</v>
+      <c r="D77" s="1">
+        <v>45447</v>
       </c>
       <c r="E77" t="s">
-        <v>65</v>
-      </c>
-      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>66</v>
+      </c>
+      <c r="G77">
         <v>3.2741524630000001</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>24.252981210000002</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C78">
         <v>89785.8</v>
       </c>
-      <c r="D78" t="s">
-        <v>9</v>
+      <c r="D78" s="1">
+        <v>45378</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78">
         <v>8.0463307549999996</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>59.602450040000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G78" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="VAD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6cbc0c5a-d948-46e5-8624-1bad210f77c7" xsi:nil="true"/>
     <SharedWithUsers xmlns="6cbc0c5a-d948-46e5-8624-1bad210f77c7">
       <UserInfo>
         <DisplayName/>
@@ -2518,10 +2732,6 @@
         <AccountType/>
       </UserInfo>
     </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6cbc0c5a-d948-46e5-8624-1bad210f77c7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -2791,13 +3001,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8682F388-0D01-401E-A5EA-680F9B15054E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F6F3900-E85E-4EBE-9ED4-197488F3D3FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{481D836B-B44F-4071-9DF4-69B4BD6A062F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{946CD9A8-BCBA-4D87-B3B1-1C411218535A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7392CB77-8E91-4B60-8739-E09B0145C631}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C8A094-F8A5-4E92-B6A2-780D1C08CA65}"/>
 </file>